--- a/ghg epds.xlsx
+++ b/ghg epds.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emilnygaardeik/Documents/Industrial_Ecology/V_2026/MFA2/Project/TEP4290-project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0721B479-5E22-814D-8AA8-83C3801ACF6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3997F7AE-3770-8448-914D-06B5F25A8427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{FBAB0AC1-3E03-C940-B006-218CDA89644B}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15940" xr2:uid="{FBAB0AC1-3E03-C940-B006-218CDA89644B}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark1" sheetId="1" r:id="rId1"/>
@@ -169,8 +169,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="170" formatCode="0.000"/>
-    <numFmt numFmtId="171" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -232,12 +232,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
